--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/FLORIDA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/FLORIDA_2020.xlsx
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C146">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C165">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C240">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C300">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C330">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C340">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C350">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C441">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C503">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C508">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C597">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C810">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C864">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C865">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C908">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C914">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C1032">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C1139">
